--- a/survey_templates/047_library_services_evaluation_form--survey_templates.xlsx
+++ b/survey_templates/047_library_services_evaluation_form--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>How did you feel about your visit to our library?</t>
+          <t>What were your experiences with our library services?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>service_quality_assessment</t>
+          <t>page_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>How would you rate the quality of our library services?</t>
+          <t>How friendly were the library staff?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>staff_friendliness_assessment</t>
+          <t>page_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>How friendly were the library staff?</t>
+          <t>How much time did you spend at the library?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,40 +584,40 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>time_spent_at_library</t>
+          <t>page_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>How much time did you spend at the library?</t>
+          <t>Do you have any suggestions for improving our library services?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>time_spent_at_library</t>
+          <t>page_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>How much time did you spend at the library?</t>
+          <t>Can we contact you?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,200 +635,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>library_facilities_condition</t>
+          <t>page_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>What did you think of the library facilities?</t>
+          <t>What do you expect from our library in the future?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>suggestions</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Do you have any suggestions for improving our library services?</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>contact_information</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Can we contact you?</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>contact_information</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Can we contact you?</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>contact_information</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Can we contact you?</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>phone_number</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>phone_number</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>phone_number</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>page_2</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>What do you expect from our library in the future?</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -845,12 +661,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -873,153 +689,68 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>service_quality_assessment_choices</t>
+          <t>page_2_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>service_quality_assessment_choices</t>
+          <t>page_2_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>service_quality_assessment_choices</t>
+          <t>page_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'satisfactory'}</t>
+          <t>satisfactory</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Satisfactory'}</t>
+          <t>Satisfactory</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>service_quality_assessment_choices</t>
+          <t>page_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Poor'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>staff_friendliness_assessment_choices</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>{'value':_'extremely_friendly'}</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>{'value': 'Extremely friendly'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>staff_friendliness_assessment_choices</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>{'value':_'somewhat_friendly'}</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>{'value': 'Somewhat friendly'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>staff_friendliness_assessment_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{'value':_'neutral'}</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>{'value': 'Neutral'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>staff_friendliness_assessment_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>{'value':_'somewhat_unfriendly'}</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>{'value': 'Somewhat unfriendly'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>staff_friendliness_assessment_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>{'value':_'extremely_unfriendly'}</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>{'value': 'Extremely unfriendly'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
